--- a/reports/ifrs9_ecl_summary_model.xlsx
+++ b/reports/ifrs9_ecl_summary_model.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: 2026-08-17 23:36:27 | Portfolio: Retail &amp; SME Loans</t>
+          <t>Report Generated: 2026-08-19 13:51:00 | Portfolio: Retail &amp; SME Loans</t>
         </is>
       </c>
     </row>

--- a/reports/ifrs9_ecl_summary_model.xlsx
+++ b/reports/ifrs9_ecl_summary_model.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: 2026-08-19 13:51:00 | Portfolio: Retail &amp; SME Loans</t>
+          <t>Report Generated: 2026-08-19 14:26:38 | Portfolio: Retail &amp; SME Loans</t>
         </is>
       </c>
     </row>
